--- a/data/data_monitoreo_cruz_pampa_yapatera.xlsx
+++ b/data/data_monitoreo_cruz_pampa_yapatera.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>165</v>
+        <v>280</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>163</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4">
@@ -467,17 +467,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>146</v>
+        <v>266</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIMA CARMEN KAREN DEL MILAGRO</t>
+          <t>ALZAMORA CHERRES SIRLEY YASMIN</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>146</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
@@ -487,27 +487,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>135</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ALZAMORA CHERRES SIRLEY YASMIN</t>
+          <t>PULACHE LAZO VILMA YOHANA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>130</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PULACHE LAZO VILMA YOHANA</t>
+          <t>NIMA CARMEN KAREN DEL MILAGRO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>213</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>120</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>116</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_cruz_pampa_yapatera.xlsx
+++ b/data/data_monitoreo_cruz_pampa_yapatera.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_cruz_pampa_yapatera.xlsx
+++ b/data/data_monitoreo_cruz_pampa_yapatera.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>281</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>274</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>234</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -538,6 +538,16 @@
       </c>
       <c r="B11" t="n">
         <v>174</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NIMA CRUZ ANA GRACIELA</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_monitoreo_cruz_pampa_yapatera.xlsx
+++ b/data/data_monitoreo_cruz_pampa_yapatera.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>290</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3">
@@ -457,27 +457,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PAZ ANASTACIO JUANITA ROSA</t>
+          <t>ALZAMORA CHERRES SIRLEY YASMIN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ALZAMORA CHERRES SIRLEY YASMIN</t>
+          <t>PAZ ANASTACIO JUANITA ROSA</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>253</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>219</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
